--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104491_W4.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104491_W4.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.6794</v>
+        <v>7.7776</v>
       </c>
       <c r="E2" t="n">
-        <v>5.6896</v>
+        <v>5.6912</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9899</v>
+        <v>2.0864</v>
       </c>
       <c r="G2" t="n">
-        <v>6.2153</v>
+        <v>6.1862</v>
       </c>
       <c r="H2" t="n">
-        <v>4.0564</v>
+        <v>4.0418</v>
       </c>
       <c r="I2" t="n">
-        <v>2.159</v>
+        <v>2.1444</v>
       </c>
       <c r="J2" t="n">
-        <v>5.9151</v>
+        <v>5.8565</v>
       </c>
       <c r="K2" t="n">
-        <v>4.9557</v>
+        <v>4.919</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9594</v>
+        <v>0.9375</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3002</v>
+        <v>0.3297</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.8993</v>
+        <v>-0.8772</v>
       </c>
       <c r="O2" t="n">
-        <v>1.1995</v>
+        <v>1.2069</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R2" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S2" t="n">
-        <v>0.32</v>
+        <v>0.4531</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1179</v>
+        <v>-0.0468</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4379</v>
+        <v>0.4999</v>
       </c>
       <c r="V2" t="n">
-        <v>1.1441</v>
+        <v>1.1383</v>
       </c>
       <c r="W2" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1093</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3795</v>
+        <v>3.4869</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3561</v>
+        <v>3.3255</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0235</v>
+        <v>0.1613</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5688</v>
+        <v>0.5782</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0176</v>
+        <v>-0.0009</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5864</v>
+        <v>0.5790999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>1.7026</v>
+        <v>1.6815</v>
       </c>
       <c r="K3" t="n">
-        <v>1.039</v>
+        <v>1.0342</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6636</v>
+        <v>0.6473</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.1338</v>
+        <v>-1.1032</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.0566</v>
+        <v>-1.0351</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0772</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R3" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3076</v>
+        <v>0.403</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4657</v>
+        <v>-0.465</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7733</v>
+        <v>0.868</v>
       </c>
       <c r="V3" t="n">
-        <v>1.369</v>
+        <v>1.3675</v>
       </c>
       <c r="W3" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.977</v>
+        <v>-0.9692</v>
       </c>
     </row>
     <row r="4">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4796</v>
+        <v>1.3005</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5467</v>
+        <v>1.4012</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.06710000000000001</v>
+        <v>-0.1007</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3838</v>
+        <v>0.3855</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3304</v>
+        <v>0.3303</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0533</v>
+        <v>0.0552</v>
       </c>
       <c r="J4" t="n">
-        <v>1.6431</v>
+        <v>1.6178</v>
       </c>
       <c r="K4" t="n">
-        <v>1.198</v>
+        <v>1.1786</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4451</v>
+        <v>0.4392</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.2593</v>
+        <v>-1.2323</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8675</v>
+        <v>-0.8483000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3918</v>
+        <v>-0.384</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.199</v>
+        <v>-0.3809</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2571</v>
+        <v>-0.3743</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0581</v>
+        <v>-0.0066</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7504999999999999</v>
+        <v>0.4505</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.9479</v>
+        <v>-1.9075</v>
       </c>
       <c r="F5" t="n">
-        <v>2.6984</v>
+        <v>2.358</v>
       </c>
       <c r="G5" t="n">
-        <v>2.441</v>
+        <v>2.4546</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3779</v>
+        <v>0.3899</v>
       </c>
       <c r="I5" t="n">
-        <v>2.0631</v>
+        <v>2.0647</v>
       </c>
       <c r="J5" t="n">
-        <v>1.8689</v>
+        <v>1.8511</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7895</v>
+        <v>0.7789</v>
       </c>
       <c r="L5" t="n">
-        <v>1.0795</v>
+        <v>1.0722</v>
       </c>
       <c r="M5" t="n">
-        <v>0.572</v>
+        <v>0.6035</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4116</v>
+        <v>-0.389</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9837</v>
+        <v>0.9925</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R5" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6871</v>
+        <v>0.3812</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1875</v>
+        <v>-0.1165</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8746</v>
+        <v>0.4977</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1093</v>
+        <v>-0.1089</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1093</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3441</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.1578</v>
+        <v>-1.4792</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5019</v>
+        <v>1.5423</v>
       </c>
       <c r="G6" t="n">
-        <v>2.7941</v>
+        <v>2.7962</v>
       </c>
       <c r="H6" t="n">
-        <v>2.013</v>
+        <v>2.0079</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7811</v>
+        <v>0.7883</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7184</v>
+        <v>1.69</v>
       </c>
       <c r="K6" t="n">
-        <v>1.6065</v>
+        <v>1.5783</v>
       </c>
       <c r="L6" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M6" t="n">
-        <v>1.0757</v>
+        <v>1.1062</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4065</v>
+        <v>0.4296</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6691</v>
+        <v>0.6766</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7501</v>
+        <v>0.467</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3902</v>
+        <v>0.1087</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3599</v>
+        <v>0.3583</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.5195</v>
+        <v>-2.5171</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.7483</v>
+        <v>-1.7432</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1926</v>
+        <v>-0.0461</v>
       </c>
       <c r="E7" t="n">
-        <v>0.07290000000000001</v>
+        <v>-0.0558</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2655</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.1122</v>
+        <v>-1.1059</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4085</v>
+        <v>-0.3997</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7037</v>
+        <v>-0.7062</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0179</v>
+        <v>-0.0299</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0968</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.1147</v>
+        <v>-0.1194</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.0944</v>
+        <v>-1.0759</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5053</v>
+        <v>-0.4891</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5891</v>
+        <v>-0.5868</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3714</v>
+        <v>-0.2393</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0907</v>
+        <v>-0.0258</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4621</v>
+        <v>-0.2135</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6105</v>
+        <v>0.6162</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6105</v>
+        <v>0.6162</v>
       </c>
     </row>
     <row r="8">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3984</v>
+        <v>-0.9172</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6243</v>
+        <v>-1.1984</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2258</v>
+        <v>0.2812</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.6776</v>
+        <v>-1.6917</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.085</v>
+        <v>-3.0901</v>
       </c>
       <c r="I8" t="n">
-        <v>1.4073</v>
+        <v>1.3984</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.8391999999999999</v>
+        <v>-0.8751</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.7369</v>
+        <v>-2.7589</v>
       </c>
       <c r="L8" t="n">
-        <v>1.8977</v>
+        <v>1.8837</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8384</v>
+        <v>-0.8166</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.348</v>
+        <v>-0.3312</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4904</v>
+        <v>-0.4854</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9742</v>
+        <v>-0.4727</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9043</v>
+        <v>-0.4324</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0699</v>
+        <v>-0.0403</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0292</v>
+        <v>-2.0882</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.9259</v>
+        <v>-4.9003</v>
       </c>
       <c r="F9" t="n">
-        <v>2.8967</v>
+        <v>2.812</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7209</v>
+        <v>-0.7157</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.417</v>
+        <v>-0.4165</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3038</v>
+        <v>-0.2992</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.0611</v>
+        <v>-1.0903</v>
       </c>
       <c r="K9" t="n">
-        <v>0.325</v>
+        <v>0.3028</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.3861</v>
+        <v>-1.3931</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3403</v>
+        <v>0.3746</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.742</v>
+        <v>-0.7193000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>1.0823</v>
+        <v>1.0939</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4549</v>
+        <v>0.3997</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3962</v>
+        <v>-0.3256</v>
       </c>
       <c r="U9" t="n">
-        <v>0.851</v>
+        <v>0.7252999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0515</v>
+        <v>0.0488</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1093</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7649</v>
+        <v>-2.2391</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0281</v>
+        <v>-0.8086</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.7369</v>
+        <v>-1.4306</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2097</v>
+        <v>0.223</v>
       </c>
       <c r="H10" t="n">
-        <v>0.199</v>
+        <v>0.2064</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0107</v>
+        <v>0.0166</v>
       </c>
       <c r="J10" t="n">
-        <v>1.8663</v>
+        <v>1.8582</v>
       </c>
       <c r="K10" t="n">
-        <v>1.6797</v>
+        <v>1.672</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1866</v>
+        <v>0.1862</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.6566</v>
+        <v>-1.6351</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.4807</v>
+        <v>-1.4656</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1759</v>
+        <v>-0.1695</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8405</v>
+        <v>-0.324</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6261</v>
+        <v>-0.3904</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2144</v>
+        <v>0.0664</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.7925</v>
+        <v>-2.9857</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.0678</v>
+        <v>-3.1294</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2753</v>
+        <v>0.1437</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.1702</v>
+        <v>-2.1623</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.928</v>
+        <v>-0.9167999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.2422</v>
+        <v>-1.2455</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.094</v>
+        <v>-2.1048</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.5959</v>
+        <v>-0.6</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.4981</v>
+        <v>-1.5048</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0762</v>
+        <v>-0.0574</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3321</v>
+        <v>-0.3168</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2559</v>
+        <v>0.2593</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4703</v>
+        <v>0.266</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1603</v>
+        <v>0.1136</v>
       </c>
       <c r="U11" t="n">
-        <v>0.31</v>
+        <v>0.1524</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.455500000000002</v>
+        <v>4.8024</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.0865</v>
+        <v>-3.061299999999998</v>
       </c>
       <c r="F12" t="n">
-        <v>7.542</v>
+        <v>7.863200000000002</v>
       </c>
       <c r="G12" t="n">
-        <v>6.931800000000001</v>
+        <v>6.9481</v>
       </c>
       <c r="H12" t="n">
-        <v>2.1206</v>
+        <v>2.1523</v>
       </c>
       <c r="I12" t="n">
-        <v>4.811199999999999</v>
+        <v>4.795800000000002</v>
       </c>
       <c r="J12" t="n">
-        <v>10.7022</v>
+        <v>10.455</v>
       </c>
       <c r="K12" t="n">
-        <v>8.3574</v>
+        <v>8.1943</v>
       </c>
       <c r="L12" t="n">
-        <v>2.344999999999999</v>
+        <v>2.2605</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.7705</v>
+        <v>-3.5065</v>
       </c>
       <c r="N12" t="n">
-        <v>-6.236599999999999</v>
+        <v>-6.042</v>
       </c>
       <c r="O12" t="n">
-        <v>2.4661</v>
+        <v>2.5354</v>
       </c>
       <c r="P12" t="n">
-        <v>-3.4024</v>
+        <v>-3.4144</v>
       </c>
       <c r="Q12" t="n">
-        <v>-15.8783</v>
+        <v>-15.9342</v>
       </c>
       <c r="R12" t="n">
-        <v>12.476</v>
+        <v>12.52</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6049</v>
+        <v>0.9531000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.3136</v>
+        <v>-1.9545</v>
       </c>
       <c r="U12" t="n">
-        <v>2.918400000000001</v>
+        <v>2.9076</v>
       </c>
       <c r="V12" t="n">
-        <v>0.3214000000000001</v>
+        <v>0.3156000000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>4.4031</v>
+        <v>4.3728</v>
       </c>
       <c r="X12" t="n">
-        <v>-4.0817</v>
+        <v>-4.0571</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.6824</v>
+        <v>5.7455</v>
       </c>
       <c r="E13" t="n">
-        <v>3.4095</v>
+        <v>3.966</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2729</v>
+        <v>1.7795</v>
       </c>
       <c r="G13" t="n">
-        <v>1.2938</v>
+        <v>1.2922</v>
       </c>
       <c r="H13" t="n">
-        <v>0.71</v>
+        <v>0.7067</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5838</v>
+        <v>0.5855</v>
       </c>
       <c r="J13" t="n">
-        <v>2.953</v>
+        <v>2.9245</v>
       </c>
       <c r="K13" t="n">
-        <v>1.3884</v>
+        <v>1.3682</v>
       </c>
       <c r="L13" t="n">
-        <v>1.5646</v>
+        <v>1.5563</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.6593</v>
+        <v>-1.6323</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.6785</v>
+        <v>-0.6615</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.9808</v>
+        <v>-0.9708</v>
       </c>
       <c r="P13" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.7436</v>
+        <v>-0.6864</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1825</v>
+        <v>-0.5927</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5610000000000001</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>2.4102</v>
+        <v>2.4082</v>
       </c>
       <c r="W13" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X13" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="14">
@@ -1501,58 +1501,58 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.1404</v>
+        <v>2.1255</v>
       </c>
       <c r="E14" t="n">
-        <v>1.0867</v>
+        <v>1.0791</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0537</v>
+        <v>1.0464</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3284</v>
+        <v>0.3382</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.218</v>
+        <v>-0.2101</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5464</v>
+        <v>0.5483</v>
       </c>
       <c r="J14" t="n">
-        <v>1.1351</v>
+        <v>1.1259</v>
       </c>
       <c r="K14" t="n">
-        <v>0.7272999999999999</v>
+        <v>0.7239</v>
       </c>
       <c r="L14" t="n">
-        <v>0.4078</v>
+        <v>0.4019</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.8066</v>
+        <v>-0.7877</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.9453</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1387</v>
+        <v>0.1463</v>
       </c>
       <c r="P14" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0027</v>
+        <v>-0.0338</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0484</v>
+        <v>-0.0468</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0457</v>
+        <v>0.013</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.66</v>
+        <v>1.1277</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8766</v>
+        <v>0.2806</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7834</v>
+        <v>0.8472</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0511</v>
+        <v>-0.0327</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4846</v>
+        <v>0.499</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5357</v>
+        <v>-0.5316</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3473</v>
+        <v>0.339</v>
       </c>
       <c r="K15" t="n">
-        <v>1.0217</v>
+        <v>1.017</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6744</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3984</v>
+        <v>-0.3717</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5371</v>
+        <v>-0.518</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1387</v>
+        <v>0.1463</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9645</v>
+        <v>0.4076</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5293</v>
+        <v>-0.0585</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4352</v>
+        <v>0.4661</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5113</v>
+        <v>0.9242</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1905</v>
+        <v>0.2471</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3208</v>
+        <v>0.6772</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5944</v>
+        <v>0.5746</v>
       </c>
       <c r="H16" t="n">
-        <v>1.8313</v>
+        <v>1.8187</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.2369</v>
+        <v>-1.2442</v>
       </c>
       <c r="J16" t="n">
-        <v>2.5173</v>
+        <v>2.4646</v>
       </c>
       <c r="K16" t="n">
-        <v>2.7147</v>
+        <v>2.6815</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.1974</v>
+        <v>-0.2169</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.9229</v>
+        <v>-1.8901</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8834</v>
+        <v>-0.8628</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.0395</v>
+        <v>-1.0273</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R16" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9224</v>
+        <v>-0.4926</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6049</v>
+        <v>-0.486</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3176</v>
+        <v>-0.0066</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="17">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0185</v>
+        <v>0.7589</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0004</v>
+        <v>0.554</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0189</v>
+        <v>0.2049</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.248</v>
+        <v>-1.2539</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2192</v>
+        <v>-0.2292</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.0289</v>
+        <v>-1.0247</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6655</v>
+        <v>-0.6966</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.0284</v>
+        <v>-0.0559</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6371</v>
+        <v>-0.6407</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5825</v>
+        <v>-0.5573</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1908</v>
+        <v>-0.1733</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3918</v>
+        <v>-0.384</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7334000000000001</v>
+        <v>0.0128</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9739</v>
+        <v>-0.3836</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2404</v>
+        <v>0.3964</v>
       </c>
       <c r="V17" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W17" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="18">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3703</v>
+        <v>-0.2483</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1045</v>
+        <v>0.0135</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2658</v>
+        <v>-0.2618</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3703</v>
+        <v>-0.3668</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0028</v>
+        <v>0.0056</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.405</v>
+        <v>-0.4012</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0318</v>
+        <v>-0.0289</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2268</v>
+        <v>-0.1092</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1391</v>
+        <v>-0.021</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0877</v>
+        <v>-0.0882</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7016</v>
+        <v>-1.0022</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5306999999999999</v>
+        <v>-0.6674</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1709</v>
+        <v>-0.3348</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.4157</v>
+        <v>-0.4123</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8369</v>
+        <v>-0.8386</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4212</v>
+        <v>0.4263</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7214</v>
+        <v>0.7057</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1243</v>
+        <v>0.1099</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5971</v>
+        <v>0.5958</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.1371</v>
+        <v>-1.118</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-0.9485</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1759</v>
+        <v>-0.1695</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3285</v>
+        <v>0.0232</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1179</v>
+        <v>-0.2349</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4464</v>
+        <v>0.2581</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="20">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6381</v>
+        <v>-1.3827</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8163</v>
+        <v>0.9265</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.4544</v>
+        <v>-2.3092</v>
       </c>
       <c r="G20" t="n">
-        <v>0.108</v>
+        <v>0.1146</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3665</v>
+        <v>0.3676</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2585</v>
+        <v>-0.253</v>
       </c>
       <c r="J20" t="n">
-        <v>1.5119</v>
+        <v>1.5051</v>
       </c>
       <c r="K20" t="n">
-        <v>1.4373</v>
+        <v>1.4307</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.4039</v>
+        <v>-1.3906</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.0708</v>
+        <v>-1.0631</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3331</v>
+        <v>-0.3275</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2412</v>
+        <v>-1.0012</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6956</v>
+        <v>-0.5786</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5456</v>
+        <v>-0.4226</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. JOKSIMOVIC</t>
+          <t>M. NOWELL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1395</v>
+        <v>-1.8146</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.025</v>
+        <v>-1.3834</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1145</v>
+        <v>-0.4312</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.9567</v>
+        <v>0.0193</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.114</v>
+        <v>0.4482</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1573</v>
+        <v>-0.4289</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.7517</v>
+        <v>0.0755</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.7517</v>
+        <v>0.8651</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>-0.7896</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.205</v>
+        <v>-0.0562</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3622</v>
+        <v>-0.4169</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1573</v>
+        <v>0.3608</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.9073</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R21" t="n">
-        <v>0.2268</v>
+        <v>0.4553</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2755</v>
+        <v>-0.0128</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1391</v>
+        <v>-0.272</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1364</v>
+        <v>0.2592</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>H. DIALLO</t>
+          <t>S. JOKSIMOVIC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2629</v>
+        <v>-1.9936</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.9863</v>
+        <v>-1.9143</v>
       </c>
       <c r="F22" t="n">
-        <v>2.7234</v>
+        <v>-0.0793</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.1223</v>
+        <v>-0.9564</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3841</v>
+        <v>-1.1143</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.5064</v>
+        <v>0.1579</v>
       </c>
       <c r="J22" t="n">
-        <v>1.4674</v>
+        <v>-0.7552</v>
       </c>
       <c r="K22" t="n">
-        <v>1.582</v>
+        <v>-0.7552</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.1147</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.5897</v>
+        <v>-0.2012</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.198</v>
+        <v>-0.3592</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.3918</v>
+        <v>0.1579</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.0415</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.5367</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>2.4952</v>
+        <v>0.2276</v>
       </c>
       <c r="S22" t="n">
-        <v>1.6041</v>
+        <v>-0.1266</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5353</v>
+        <v>-0.021</v>
       </c>
       <c r="U22" t="n">
-        <v>2.1394</v>
+        <v>-0.1057</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.7032</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>-1.3817</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.3214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. NOWELL</t>
+          <t>H. DIALLO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.5073</v>
+        <v>-3.2295</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.712</v>
+        <v>-4.9313</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7952</v>
+        <v>1.7018</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0184</v>
+        <v>-0.1349</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4502</v>
+        <v>0.3685</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.4318</v>
+        <v>-0.5034</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0897</v>
+        <v>1.4277</v>
       </c>
       <c r="K23" t="n">
-        <v>0.876</v>
+        <v>1.5471</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.7864</v>
+        <v>-0.1194</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.0712</v>
+        <v>-1.5626</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4258</v>
+        <v>-1.1786</v>
       </c>
       <c r="O23" t="n">
-        <v>0.3546</v>
+        <v>-0.384</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.8147</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2683</v>
+        <v>-4.5526</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4537</v>
+        <v>2.5039</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.711</v>
+        <v>0.6597</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6261</v>
+        <v>-0.4163</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.08500000000000001</v>
+        <v>1.076</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-1.7057</v>
       </c>
       <c r="W23" t="n">
-        <v>1.0927</v>
+        <v>-1.3901</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0927</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.8485</v>
+        <v>-5.4648</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.5628</v>
+        <v>-6.0338</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7143</v>
+        <v>0.569</v>
       </c>
       <c r="G24" t="n">
-        <v>-6.1106</v>
+        <v>-6.1301</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.9622</v>
+        <v>-3.9743</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.1485</v>
+        <v>-2.1558</v>
       </c>
       <c r="J24" t="n">
-        <v>-5.59</v>
+        <v>-5.6441</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.8897</v>
+        <v>-2.9247</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.7003</v>
+        <v>-2.7194</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.5206</v>
+        <v>-0.486</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.0725</v>
+        <v>-1.0496</v>
       </c>
       <c r="O24" t="n">
-        <v>0.5518999999999999</v>
+        <v>0.5636</v>
       </c>
       <c r="P24" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S24" t="n">
-        <v>2.3548</v>
+        <v>0.7548</v>
       </c>
       <c r="T24" t="n">
-        <v>1.6151</v>
+        <v>0.2037</v>
       </c>
       <c r="U24" t="n">
-        <v>0.7398</v>
+        <v>0.551</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W24" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.455599999999999</v>
+        <v>-4.4539</v>
       </c>
       <c r="E25" t="n">
-        <v>-7.5421</v>
+        <v>-7.8634</v>
       </c>
       <c r="F25" t="n">
-        <v>3.0866</v>
+        <v>3.4097</v>
       </c>
       <c r="G25" t="n">
-        <v>-6.931699999999999</v>
+        <v>-6.9482</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.1208</v>
+        <v>-2.1522</v>
       </c>
       <c r="I25" t="n">
-        <v>-4.811199999999999</v>
+        <v>-4.795999999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>3.7705</v>
+        <v>3.506599999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>6.236500000000001</v>
+        <v>6.042100000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.4662</v>
+        <v>-2.5354</v>
       </c>
       <c r="M25" t="n">
-        <v>-10.7022</v>
+        <v>-10.4549</v>
       </c>
       <c r="N25" t="n">
-        <v>-8.3574</v>
+        <v>-8.194400000000002</v>
       </c>
       <c r="O25" t="n">
-        <v>-2.3449</v>
+        <v>-2.2606</v>
       </c>
       <c r="P25" t="n">
-        <v>3.402499999999999</v>
+        <v>3.4145</v>
       </c>
       <c r="Q25" t="n">
-        <v>-12.4759</v>
+        <v>-12.5198</v>
       </c>
       <c r="R25" t="n">
-        <v>15.8783</v>
+        <v>15.9342</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.6046999999999998</v>
+        <v>-0.6044999999999997</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.9184</v>
+        <v>-2.9077</v>
       </c>
       <c r="U25" t="n">
-        <v>2.3136</v>
+        <v>2.303</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.3214000000000001</v>
+        <v>-0.3155000000000001</v>
       </c>
       <c r="W25" t="n">
-        <v>4.0816</v>
+        <v>4.057200000000001</v>
       </c>
       <c r="X25" t="n">
-        <v>-4.403</v>
+        <v>-4.3729</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104491_W4.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104491_W4.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104491_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.9692</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104491_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104491_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104491_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.7432</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104491_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0.6162</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104491_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104491_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104491_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104491_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104491_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-4.0571</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104491_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104491_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104491_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104491_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104491_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104491_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104491_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104491_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104491_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104491_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104491_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104491_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-4.3729</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
